--- a/codecoin_database.xlsx
+++ b/codecoin_database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="spaces" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="events" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="bugjam" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spaces" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="events" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bugjam" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -70,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -80,6 +80,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1172,13 +1175,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>คลังคำถาม | level: 1=ตอนซื้อ(ง่าย) 2=อัปเกรดชำนาญ 3=อัปเกรดผู้เชี่ยวชาญ | answer กรอก a/b/c/d ตัวเดียว | time_limit วินาที (เว้นว่าง=ไม่จับเวลา) | แถวยังไม่เสร็จใส่ DRAFT หน้าโจทย์</t>
+          <t>คลังคำถาม | level: 1=ตอนซื้อ(ง่าย) 2=อัปเกรดชำนาญ 3=อัปเกรดผู้เชี่ยวชาญ 4=โหมดมั่นใจ | answer กรอก a/b/c/d ตัวเดียว | time_limit วินาที (เว้นว่าง=ไม่จับเวลา) | แถวยังไม่เสร็จใส่ DRAFT หน้าโจทย์ || qtype เว้นว่าง = ข้อสอบเลือกตอบแบบเดิม (ปกติใช้แบบนี้) ถ้าใส่ hotspot/colorwheel/linepick ให้เว้น choice_a-d ว่างทั้งหมด แล้วกรอก answer ตามรูปแบบด้านล่าง | hotspot: asset=ชื่อภาพ, answer=x,y,รัศมี เป็นเปอร์เซ็นต์ของภาพ, payload=ชื่อชิ้นส่วนที่จะเฉลยตอนตอบผิด | colorwheel: asset=wheel:ชื่อสีโจทย์, answer=องศาคำตอบ 0-359, payload=ระยะผ่อนผันเป็นองศา | linepick: payload=โค้ด ขึ้นบรรทัดใหม่ด้วย Alt+Enter, answer=เลขบรรทัดที่ผิด</t>
         </is>
       </c>
     </row>
@@ -1233,6 +1241,21 @@
           <t>time_limit</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>qtype</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1496,31 +1519,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Python ใช้อะไรแบ่งบล็อกโค้ด?</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>การย่อหน้า (indent)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>เครื่องหมาย ;</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>วงเล็บปีกกา { }</t>
+          <t>แตะบรรทัดที่ย่อหน้า (indent) ผิด</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>linepick</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>def total_score(scores):
+    total = 0
+    for s in scores:
+    total = total + s
+    return total</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1954,27 +1976,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>สีคู่ตรงข้าม (Complementary) ให้ความรู้สึกแบบใด?</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>โดดเด่น สะดุดตา</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>มองไม่เห็น</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ง่วงนอน</t>
+          <t>แตะสีคู่ตรงข้าม (Complementary) ของสีส้ม</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>15</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>colorwheel</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>wheel:orange</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -3282,27 +3307,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CPU ติดตั้งลงบนส่วนใดของเมนบอร์ด?</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Socket</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>RAM Slot</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>ที่วางแก้วน้ำ</t>
+          <t>แตะตำแหน่งที่ใช้ติดตั้ง CPU บนเมนบอร์ด</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>44,23,10</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>15</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>motherboard</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>CPU Socket</t>
         </is>
       </c>
     </row>
@@ -3697,31 +3725,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>สายไฟเส้นใหญ่ที่สุดที่เสียบเข้าเมนบอร์ดโดยตรงคือสายใด?</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>สาย 24-pin</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>สาย LAN</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>สายหูฟัง</t>
+          <t>แตะช่องที่ใช้เสียบสายไฟหลัก ATX 24-pin</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>91,33,8</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>motherboard</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>ATX 24-pin</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -4576,6 +4604,49 @@
       </c>
       <c r="J82" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>hardware_02_L1_03</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>hardware_02</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>แตะสลอตที่ใช้ติดตั้ง RAM บนเมนบอร์ด</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>70,31,11</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>15</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>motherboard</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>DIMM Slots (สลอต RAM)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/codecoin_database.xlsx
+++ b/codecoin_database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spaces" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="events" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bugjam" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="spaces" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="events" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="bugjam" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ข้อมูลช่องทรัพย์สิน 16 ช่อง | ห้ามแก้ชื่อคอลัมน์ | space_id ตัวพิมพ์เล็ก+underscore | content_th ไม่เกิน ~350 ตัวอักษร (อ่านจบใน 1 นาที)</t>
+          <t>ข้อมูลช่องทรัพย์สิน 16 ช่อง (โซนละ 4: coding / office / design / hardware) | ห้ามแก้ชื่อคอลัมน์และห้ามสลับลำดับคอลัมน์ | space_id = {zone}_{01-04} ตัวพิมพ์เล็ก+underscore ห้ามเปลี่ยน เพราะ QR บนกระดานและการ์ดทรัพย์สินอ้างค่านี้ | price = ราคาซื้อ · rent_L0 = ค่าเช่าก่อนอัปเกรด · rent_L1 / L2 / L3 = ค่าเช่าระดับมือใหม่ / ชำนาญ / ผู้เชี่ยวชาญ · upgrade_cost = ค่าอัปเกรดต่อครั้ง (ลด 20% จากรุ่นแรกตั้งแต่ REV 2.1 — ตัวเลขปัจจุบันคือของที่พิมพ์ลงการ์ดแล้ว) | ตัวเลขกรอกเป็นจำนวนเต็ม ไม่ใส่คอมมา | content_th ไม่เกิน ~350 ตัวอักษร (อ่านจบใน 1 นาที) | แก้ไฟล์นี้เสร็จให้รัน  py scripts/build_data.py  เพื่อสร้าง data.json ใหม่ — ห้ามแก้ data.json ด้วยมือ</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>คลังคำถาม | level: 1=ตอนซื้อ(ง่าย) 2=อัปเกรดชำนาญ 3=อัปเกรดผู้เชี่ยวชาญ 4=โหมดมั่นใจ | answer กรอก a/b/c/d ตัวเดียว | time_limit วินาที (เว้นว่าง=ไม่จับเวลา) | แถวยังไม่เสร็จใส่ DRAFT หน้าโจทย์ || qtype เว้นว่าง = ข้อสอบเลือกตอบแบบเดิม (ปกติใช้แบบนี้) ถ้าใส่ hotspot/colorwheel/linepick ให้เว้น choice_a-d ว่างทั้งหมด แล้วกรอก answer ตามรูปแบบด้านล่าง | hotspot: asset=ชื่อภาพ, answer=x,y,รัศมี เป็นเปอร์เซ็นต์ของภาพ, payload=ชื่อชิ้นส่วนที่จะเฉลยตอนตอบผิด | colorwheel: asset=wheel:ชื่อสีโจทย์, answer=องศาคำตอบ 0-359, payload=ระยะผ่อนผันเป็นองศา | linepick: payload=โค้ด ขึ้นบรรทัดใหม่ด้วย Alt+Enter, answer=เลขบรรทัดที่ผิด</t>
+          <t>คลังคำถาม 81 ข้อ (ทุกช่องมีครบ 4 ระดับ) | level: 1 = ตอนซื้อ / อัปเกรดมือใหม่ (ง่าย) · 2 = อัปเกรดชำนาญ · 3 = อัปเกรดผู้เชี่ยวชาญ · 4 = โหมดมั่นใจ 💎 (ยากที่สุด ตอบถูกลดราคา 40% ตอบผิดต้องหมุนวงล้อ ใช้เวลา 25 วิ) | answer กรอก a/b/c/d ตัวเดียว | time_limit หน่วยวินาที (เว้นว่าง = ไม่จับเวลา) | เว็บแสดงตัวเลือกตามลำดับที่กรอกในไฟล์นี้ (ไม่สลับให้) — ช่วยกระจายตำแหน่งเฉลยอย่าให้ซ้ำตำแหน่งเดิมทุกข้อ | ⚠ ตัวเลือกที่ขึ้นต้นด้วย = หรือ + ต้องพิมพ์ ' นำหน้า (เช่น '= (เท่ากับ)) ไม่งั้น Excel เก็บเป็นสูตรแล้วข้อความหายตอน build | แถวยังไม่เสร็จใส่ DRAFT หน้าโจทย์ || qtype เว้นว่าง = ข้อสอบเลือกตอบแบบเดิม (ปกติใช้แบบนี้) ถ้าใส่ hotspot / colorwheel / linepick ให้เว้น choice_a-d ว่างทั้งหมด แล้วกรอก answer ตามรูปแบบด้านล่าง (กรอกผิดรูปแบบ build_data.py จะฟ้อง error และไม่เขียน data.json) | hotspot: asset = ชื่อภาพ (ตอนนี้มีภาพเดียวคือ motherboard), answer = x,y,รัศมี เป็นเปอร์เซ็นต์ของภาพ, payload = ชื่อชิ้นส่วนที่จะเฉลยตอนตอบผิด — หาพิกัดด้วย tools/hotspot_picker.html | colorwheel: asset = wheel:ชื่อสีโจทย์, answer = องศาคำตอบ 0-359, payload = ระยะผ่อนผันเป็นองศา (1-45) | linepick: payload = โค้ด ขึ้นบรรทัดใหม่ด้วย Alt+Enter, answer = เลขบรรทัดที่ผิด (เริ่มนับ 1)</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>การ์ดเหตุการณ์ (เป้า: โซนละ 8-10 ใบ) | mechanic: simple/choice/speed/chain/minigame | effect: +1500 รับ | -800 จ่าย | skip:1 ข้ามเทิร์น | all:-500 คนอื่นจ่ายทุกคน | collect:200 เก็บจากทุกคน | bet:1000:x3|safe:+300 เลือกเสี่ยง/ชัวร์ | weight เลขมาก=ออกบ่อย</t>
+          <t>การ์ดเหตุการณ์ 20 ใบ — โซนละ 5 ใบ ครบแล้ว (พิมพ์เป็นการ์ดจริงในกล่องแล้ว ถ้าจะเพิ่ม/แก้ ต้องพิมพ์การ์ดใหม่ด้วย) | mechanic ที่เว็บรองรับ: simple = แสดงผลอย่างเดียว · choice = ให้เลือกเสี่ยง/ชัวร์ (effect ต้องเป็นแบบ bet:...|safe:...) · speed = แข่งกดตอบเร็ว 1-4 คน (เวลา 15 วิ ตั้งที่ CONFIG.speed_time_limit ในเว็บ ไม่ได้อ่านจากไฟล์นี้) · chain = ผลกระทบถึงผู้เล่นคนอื่น (หน้าจอแสดงเหมือน simple) — คำว่า minigame ยังไม่รองรับ อย่าใช้ | effect: +1500 รับ | -800 จ่าย | skip:1 ข้ามเทิร์น | all:-500 คนอื่นจ่ายทุกคน | collect:200 เก็บจากทุกคน | bet:1000:x3|safe:+300 เลือกเสี่ยง/ชัวร์ | weight เลขมาก = ออกบ่อย (ตอนนี้ simple = 2, choice/chain/speed = 1) | description_th = ข้อความเล่าเรื่อง แสดงใต้หัวข้อบนหน้าเหตุการณ์ (เว้นว่างได้แต่ควรมี)</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>โจทย์ "หาจุดผิด" ช่องติดบั๊ก ครบ 4 วิชา (เป้า: 10-15 ข้อ) | code_snippet = โค้ดหรือสถานการณ์ ขึ้นบรรทัดใหม่ด้วย Alt+Enter | answer กรอก a/b/c | ทุกข้อระดับง่าย 30 วิ</t>
+          <t>โจทย์ "หาจุดผิด" ช่องติดบั๊ก 19 ข้อ (ง่าย 15 / ยาก 4) ครบ 4 วิชา | code_snippet = โค้ดหรือสถานการณ์ ขึ้นบรรทัดใหม่ด้วย Alt+Enter | answer กรอก a/b/c (มีแค่ 3 ตัวเลือก) | difficulty กรอกได้แค่ easy หรือ hard — easy ตอบถูกออกจากช่องฟรี / hard ตอบถูกได้โบนัส 300 TechCoin (เหลือ 150 ถ้ากดดู hint) | hint = คำใบ้ 1 บรรทัด กดดูได้ครั้งเดียว ใส่ได้ทั้งข้อง่ายและข้อยาก (ข้อง่ายกดดูแล้วไม่เสียอะไร) | ตอบผิดหรือหมดเวลา = เสียค่าปรับ (ง่าย 300 / ยาก 500) และตอบได้ครั้งเดียวต่อเทิร์น | เว็บสลับตำแหน่งตัวเลือกให้เองทุกครั้ง ห้ามเขียนโจทย์อ้างตัวอักษร เช่น "ข้อ ก ถูก" | ⚠ คอลัมน์ time_limit เลิกใช้แล้ว — เวลาจริงมาจาก CONFIG ในเว็บ (ง่าย 20 วิ / ยาก 45 วิ) คงคอลัมน์ไว้เฉย ๆ</t>
         </is>
       </c>
     </row>
